--- a/artfynd/A 41022-2021 artfynd.xlsx
+++ b/artfynd/A 41022-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651209</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638370</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651220</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638309</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638575</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638891</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639181</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639447</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639530</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1945,6 +2005,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639882</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2042,6 +2107,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639904</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134640148</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2241,6 +2316,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641439</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2343,6 +2423,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134642417</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2470,6 +2555,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651202</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2597,6 +2687,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651204</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2724,6 +2819,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651205</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2851,6 +2951,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651210</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2978,6 +3083,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651214</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3105,6 +3215,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651215</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3232,6 +3347,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651218</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3359,6 +3479,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651222</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3486,6 +3611,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651225</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3613,6 +3743,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651227</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3710,6 +3845,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639267</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3807,6 +3947,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134640289</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3909,6 +4054,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638299</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4011,6 +4161,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638402</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4113,6 +4268,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638870</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4215,6 +4375,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134640396</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4317,6 +4482,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641203</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4419,6 +4589,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134642238</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4536,6 +4711,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651199</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4653,6 +4833,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651201</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4765,6 +4950,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651207</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4867,6 +5057,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641992</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4969,6 +5164,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134642425</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5071,6 +5271,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639732</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5173,6 +5378,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638414</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5275,6 +5485,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134638877</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5377,6 +5592,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639677</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5479,6 +5699,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134640410</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5581,6 +5806,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641573</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5683,6 +5913,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134642335</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5795,6 +6030,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651212</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5892,6 +6132,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134642038</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5989,6 +6234,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639282</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6086,6 +6336,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134640295</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6183,6 +6438,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641523</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6280,6 +6540,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134642225</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6377,6 +6642,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134642487</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6479,6 +6749,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134641391</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6576,6 +6851,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134639452</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6698,6 +6978,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651217</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6820,8 +7105,72 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134651219</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>